--- a/www/flightdata/xlsx/eoss-294.xlsx
+++ b/www/flightdata/xlsx/eoss-294.xlsx
@@ -3012,7 +3012,7 @@
         <v>27113.79</v>
       </c>
       <c r="I2">
-        <v>499</v>
+        <v>365</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
